--- a/06_코드/qa/manual_check/J5_수기검산_수행본_20260730.xlsx
+++ b/06_코드/qa/manual_check/J5_수기검산_수행본_20260730.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zzxxc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\zzxxc\Documents\deep_lerning\venv\AIQuant-3rd-project\06_코드\qa\manual_check\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{293F1FD3-C40D-476B-931A-16F09CB78F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2103D98-3560-4BF3-A18D-07A24632B7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3280" yWindow="3270" windowWidth="16620" windowHeight="7500" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00 시작하기" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="527">
   <si>
     <t>J-5 수기 검산 워크북</t>
   </si>
@@ -988,9 +988,6 @@
   </si>
   <si>
     <t>SEASONING_INCOMPLETE</t>
-  </si>
-  <si>
-    <t>분포에 넣을지 판단하십시오</t>
   </si>
   <si>
     <t>계산</t>
@@ -1621,6 +1618,55 @@
     <t>분포 포함?</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
+  <si>
+    <t>일치</t>
+  </si>
+  <si>
+    <t>분모 = 관측 90 − 결측 0. 룰북 189행</t>
+  </si>
+  <si>
+    <t>제외</t>
+  </si>
+  <si>
+    <t>부동소수 잔차 2.220e-16 — 허용오차 1e-6 이내</t>
+  </si>
+  <si>
+    <t>부동소수 잔차 3.553e-15 — 허용오차 1e-6 이내</t>
+  </si>
+  <si>
+    <t>부동소수 잔차 2.274e-13 — 허용오차 1e-6 이내</t>
+  </si>
+  <si>
+    <t>부동소수 잔차 5.329e-15 — 허용오차 1e-6 이내</t>
+  </si>
+  <si>
+    <t>[사후 2026-07-31] F열 전기·G열 판정은 봉인 파일 J5_코드값_봉인.xlsx 에서 QA 스크립트로 옮겼습니다. 수행 당시 손으로 옮기는 절차는 수행되지 않았습니다 (J5 결과기록 §4-b). 수기값 E열은 2026-07-30 수행분 그대로이며 수정하지 않았습니다.</t>
+  </si>
+  <si>
+    <t>[사후 2026-07-31] 한국만 개장·미국 휴장 → 공통 개장일 아님. 결정로그 323행 D-13 ⑧ '한·미 공통 개장일 기준 역산'. 이 하루가 실제로 결과를 바꾸는 구간이다.</t>
+  </si>
+  <si>
+    <t>[사후 2026-07-31] 선정일 6/30 을 세지 않고 역산한 5번째 공통 개장일. 결정로그 323행 '선정일 이전 제5거래일'. 다만 기산점(선정일 포함 여부)은 조문에 명시가 없다 — J5 결과기록 §5-d.</t>
+  </si>
+  <si>
+    <t>[사후 2026-07-31] 룰북 199행 '분포 모집단은 시장별 전체 유니버스(보통주·시즈닝 통과)'. SEASONING_INCOMPLETE 이므로 분포에서 제외. 이 판단은 수행 시점에 E25 로 기록됨.</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>[사후 2026-07-31] h=(n−1)×0.10 ≥ 1 → n ≥ 11. Seed18 은 시장별 8~9종목이므로 구조적으로 항상 1종목만 탈락한다. 현 규칙은 '유동성 하한 미달 제외'가 아니라 '최하위 1종목 제외'로 작동.</t>
+  </si>
+  <si>
+    <t>[사후 2026-07-31] US_SPACE_DEFENSE 셀에 KTOS 1종목만 남아 셀 몫 1/6 을 단독 보유. 개별종목 상한·셀 최소 종목수 규정이 룰북에 없다 — J5 결과기록 §5-c.</t>
+  </si>
+  <si>
+    <t>[사후 2026-07-31] 룰북 218행 '테마×지역 6셀 각 1/6 [확정, D-10 ②]'. 다만 같은 행의 '(1:1:1과 50:50을 동시 만족하는 유일 행렬)'은 오류다 — 자유도 2, 반례 존재 (룰북 정정 대상 6-a). 값 1/6 은 D-10 ② 채택값이므로 유지.</t>
+  </si>
+  <si>
+    <t>[사후 2026-07-31] TRADING_HALT 3일(04-08~04-10). 정지일 종가는 직전가 유지, 거래대금 0 으로 반영한다(룰북 189행 R6). 상태코드는 daily_market_state 6종 중 하나.</t>
+  </si>
+  <si>
+    <t>[사후 2026-07-31] 분할 경계일 04-13 = 신주권상장·거래재개일. 07-30 의결 PAR_VALUE_5TO1_LISTING_BOUNDARY_PILOT. 효력일(04-10)로 잡으면 종가 수준은 같으나 연변동성이 42.40% ↔ 71.77% 로 갈린다 — 두 날짜를 반드시 분리해 기록할 것.</t>
+  </si>
 </sst>
 </file>
 
@@ -1630,7 +1676,7 @@
     <numFmt numFmtId="176" formatCode="0.000000"/>
     <numFmt numFmtId="177" formatCode="#,##0.0"/>
     <numFmt numFmtId="178" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="184" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="179" formatCode="#,##0.00_ "/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -1795,7 +1841,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1834,35 +1880,36 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="184" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2210,146 +2257,146 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" s="28"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
+      <c r="A7" s="30"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A13" s="35" t="s">
+      <c r="A13" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A14" s="35" t="s">
+      <c r="A14" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A15" s="35" t="s">
+      <c r="A15" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A16" s="35" t="s">
+      <c r="A16" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" s="3" t="s">
@@ -2404,40 +2451,40 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" s="3" t="s">
@@ -2582,76 +2629,76 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A45" s="36" t="s">
+      <c r="A45" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="B45" s="29"/>
-      <c r="C45" s="29"/>
-      <c r="D45" s="29"/>
-      <c r="E45" s="29"/>
-      <c r="F45" s="29"/>
-      <c r="G45" s="29"/>
-      <c r="H45" s="29"/>
+      <c r="B45" s="31"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="31"/>
+      <c r="H45" s="31"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A46" s="35" t="s">
+      <c r="A46" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="31"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A47" s="35" t="s">
+      <c r="A47" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="29"/>
+      <c r="B47" s="31"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="31"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A48" s="35" t="s">
+      <c r="A48" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
+      <c r="B48" s="31"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="31"/>
+      <c r="H48" s="31"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A49" s="35" t="s">
+      <c r="A49" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
+      <c r="B49" s="31"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="31"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A50" s="35" t="s">
+      <c r="A50" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="B50" s="29"/>
-      <c r="C50" s="29"/>
-      <c r="D50" s="29"/>
-      <c r="E50" s="29"/>
-      <c r="F50" s="29"/>
-      <c r="G50" s="29"/>
-      <c r="H50" s="29"/>
+      <c r="B50" s="31"/>
+      <c r="C50" s="31"/>
+      <c r="D50" s="31"/>
+      <c r="E50" s="31"/>
+      <c r="F50" s="31"/>
+      <c r="G50" s="31"/>
+      <c r="H50" s="31"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" s="3" t="s">
@@ -2747,16 +2794,16 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A61" s="31" t="s">
+      <c r="A61" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
-      <c r="F61" s="29"/>
-      <c r="G61" s="29"/>
-      <c r="H61" s="29"/>
+      <c r="B61" s="31"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="31"/>
+      <c r="E61" s="31"/>
+      <c r="F61" s="31"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="31"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A63" s="3" t="s">
@@ -2767,55 +2814,44 @@
       <c r="A64" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B64" s="32"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="29"/>
+      <c r="B64" s="35"/>
+      <c r="C64" s="31"/>
+      <c r="D64" s="31"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B65" s="32"/>
-      <c r="C65" s="29"/>
-      <c r="D65" s="29"/>
+      <c r="B65" s="35"/>
+      <c r="C65" s="31"/>
+      <c r="D65" s="31"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B66" s="32"/>
-      <c r="C66" s="29"/>
-      <c r="D66" s="29"/>
+      <c r="B66" s="35"/>
+      <c r="C66" s="31"/>
+      <c r="D66" s="31"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B67" s="32"/>
-      <c r="C67" s="29"/>
-      <c r="D67" s="29"/>
+      <c r="B67" s="35"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="31"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B68" s="32"/>
-      <c r="C68" s="29"/>
-      <c r="D68" s="29"/>
+      <c r="B68" s="35"/>
+      <c r="C68" s="31"/>
+      <c r="D68" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A61:H61"/>
     <mergeCell ref="B68:D68"/>
     <mergeCell ref="A46:H46"/>
     <mergeCell ref="A27:H27"/>
@@ -2832,6 +2868,17 @@
     <mergeCell ref="B67:D67"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A61:H61"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2852,76 +2899,76 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A4" s="30" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" s="28" t="s">
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" s="34" t="s">
         <v>479</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="31" t="s">
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6" s="34" t="s">
         <v>480</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" s="31" t="s">
-        <v>481</v>
-      </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>483</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="10" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>103</v>
@@ -2932,22 +2979,22 @@
       </c>
       <c r="D10" s="7">
         <f>'09 대조표'!F10</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="12">
+        <v>46196</v>
+      </c>
+      <c r="E10" s="12" t="str">
         <f>'09 대조표'!G10</f>
-        <v>0</v>
+        <v>일치</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="10" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C11" s="7">
         <f>'09 대조표'!E11</f>
@@ -2955,22 +3002,22 @@
       </c>
       <c r="D11" s="7">
         <f>'09 대조표'!F11</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="12">
+        <v>315154781.22222221</v>
+      </c>
+      <c r="E11" s="12" t="str">
         <f>'09 대조표'!G11</f>
-        <v>0</v>
+        <v>일치</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>448</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>449</v>
       </c>
       <c r="C12" s="7">
         <f>'09 대조표'!E12</f>
@@ -2978,22 +3025,22 @@
       </c>
       <c r="D12" s="7">
         <f>'09 대조표'!F12</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="12">
+        <v>90</v>
+      </c>
+      <c r="E12" s="12" t="str">
         <f>'09 대조표'!G12</f>
-        <v>0</v>
+        <v>일치</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>451</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>452</v>
       </c>
       <c r="C13" s="7">
         <f>'09 대조표'!E13</f>
@@ -3001,45 +3048,45 @@
       </c>
       <c r="D13" s="7">
         <f>'09 대조표'!F13</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="12">
+        <v>316884754.0355556</v>
+      </c>
+      <c r="E13" s="12" t="str">
         <f>'09 대조표'!G13</f>
-        <v>0</v>
+        <v>일치</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C14" s="7" t="str">
         <f>'09 대조표'!E14</f>
         <v>제외</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="7" t="str">
         <f>'09 대조표'!F14</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="12">
+        <v>제외</v>
+      </c>
+      <c r="E14" s="12" t="str">
         <f>'09 대조표'!G14</f>
-        <v>0</v>
+        <v>일치</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>455</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>456</v>
       </c>
       <c r="C15" s="7">
         <f>'09 대조표'!E15</f>
@@ -3047,22 +3094,22 @@
       </c>
       <c r="D15" s="7">
         <f>'09 대조표'!F15</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="12">
+        <v>1</v>
+      </c>
+      <c r="E15" s="12" t="str">
         <f>'09 대조표'!G15</f>
-        <v>0</v>
+        <v>일치</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>458</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>459</v>
       </c>
       <c r="C16" s="7">
         <f>'09 대조표'!E16</f>
@@ -3070,22 +3117,22 @@
       </c>
       <c r="D16" s="7">
         <f>'09 대조표'!F16</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="12">
+        <v>11</v>
+      </c>
+      <c r="E16" s="12" t="str">
         <f>'09 대조표'!G16</f>
-        <v>0</v>
+        <v>일치</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>460</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>461</v>
       </c>
       <c r="C17" s="7">
         <f>'09 대조표'!E17</f>
@@ -3093,22 +3140,22 @@
       </c>
       <c r="D17" s="7">
         <f>'09 대조표'!F17</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="12">
+        <v>1</v>
+      </c>
+      <c r="E17" s="12" t="str">
         <f>'09 대조표'!G17</f>
-        <v>0</v>
+        <v>일치</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>463</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>464</v>
       </c>
       <c r="C18" s="7">
         <f>'09 대조표'!E18</f>
@@ -3116,22 +3163,22 @@
       </c>
       <c r="D18" s="7">
         <f>'09 대조표'!F18</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="12">
+        <v>16.666666666666661</v>
+      </c>
+      <c r="E18" s="12" t="str">
         <f>'09 대조표'!G18</f>
-        <v>0</v>
+        <v>일치</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>466</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>467</v>
       </c>
       <c r="C19" s="7">
         <f>'09 대조표'!E19</f>
@@ -3139,22 +3186,22 @@
       </c>
       <c r="D19" s="7">
         <f>'09 대조표'!F19</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="12">
+        <v>1023.8015667579469</v>
+      </c>
+      <c r="E19" s="12" t="str">
         <f>'09 대조표'!G19</f>
-        <v>0</v>
+        <v>일치</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>469</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>470</v>
       </c>
       <c r="C20" s="7">
         <f>'09 대조표'!E20</f>
@@ -3162,22 +3209,22 @@
       </c>
       <c r="D20" s="7">
         <f>'09 대조표'!F20</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="12">
+        <v>-77.258883248730953</v>
+      </c>
+      <c r="E20" s="12" t="str">
         <f>'09 대조표'!G20</f>
-        <v>0</v>
+        <v>일치</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>471</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>472</v>
       </c>
       <c r="C21" s="7">
         <f>'09 대조표'!E21</f>
@@ -3185,103 +3232,103 @@
       </c>
       <c r="D21" s="7">
         <f>'09 대조표'!F21</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="12">
+        <v>13.705583756345179</v>
+      </c>
+      <c r="E21" s="12" t="str">
         <f>'09 대조표'!G21</f>
-        <v>0</v>
+        <v>일치</v>
       </c>
       <c r="F21" s="11" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A23" s="32" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A23" s="36" t="s">
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A24" s="33" t="s">
         <v>497</v>
       </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A24" s="35" t="s">
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A25" s="33" t="s">
         <v>498</v>
       </c>
-      <c r="B24" s="29"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A25" s="35" t="s">
+      <c r="B25" s="31"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A26" s="33" t="s">
         <v>499</v>
       </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A26" s="35" t="s">
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A27" s="33" t="s">
         <v>500</v>
       </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A27" s="35" t="s">
+      <c r="B27" s="31"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A28" s="32"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A29" s="32" t="s">
         <v>501</v>
       </c>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A28" s="36"/>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A29" s="36" t="s">
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A30" s="33" t="s">
         <v>502</v>
       </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A30" s="35" t="s">
+      <c r="B30" s="31"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A31" s="33" t="s">
         <v>503</v>
       </c>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A31" s="35" t="s">
-        <v>504</v>
-      </c>
-      <c r="B31" s="29"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -3327,59 +3374,59 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="36" t="s">
+        <v>507</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="36" t="s">
         <v>508</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" s="34" t="s">
-        <v>509</v>
-      </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="37" t="s">
-        <v>510</v>
-      </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
+        <v>509</v>
+      </c>
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="30" t="s">
         <v>144</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
@@ -3520,7 +3567,9 @@
         <f t="array" ref="F16">IF(E16=0,"",SUMPRODUCT(($B$12:$B$23&gt;B16)*($B$12:$B$23&lt;=$B$23)*$E$12:$E$23))</f>
         <v/>
       </c>
-      <c r="G16" s="7"/>
+      <c r="G16" s="7" t="s">
+        <v>519</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="10">
@@ -3566,7 +3615,9 @@
         <f t="array" ref="F18">IF(E18=0,"",SUMPRODUCT(($B$12:$B$23&gt;B18)*($B$12:$B$23&lt;=$B$23)*$E$12:$E$23))</f>
         <v>5</v>
       </c>
-      <c r="G18" s="7"/>
+      <c r="G18" s="7" t="s">
+        <v>520</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="10">
@@ -3692,50 +3743,50 @@
       <c r="A26" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B26" s="33" t="s">
+      <c r="B26" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="C26" s="29"/>
+      <c r="C26" s="31"/>
       <c r="D26" s="13" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A29" s="35" t="s">
+      <c r="A29" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A30" s="35" t="s">
+      <c r="A30" s="33" t="s">
         <v>169</v>
       </c>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
+      <c r="B30" s="31"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -3914,40 +3965,40 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="30" t="s">
         <v>137</v>
       </c>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3985,59 +4036,59 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="34" t="s">
         <v>174</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
@@ -5777,7 +5828,7 @@
         <v>267852320</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G89" s="7"/>
     </row>
@@ -6054,124 +6105,117 @@
       <c r="A104" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="B104" s="38">
+      <c r="B104" s="42">
         <f>COUNT(A12:A101)</f>
         <v>90</v>
       </c>
-      <c r="C104" s="29"/>
-      <c r="D104" s="30" t="s">
+      <c r="C104" s="31"/>
+      <c r="D104" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="E104" s="39"/>
-      <c r="F104" s="39"/>
-      <c r="G104" s="40"/>
+      <c r="E104" s="40"/>
+      <c r="F104" s="40"/>
+      <c r="G104" s="41"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A105" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="B105" s="38">
+      <c r="B105" s="42">
         <f>COUNTIF(F12:F101,"TRADING_HALT")</f>
         <v>0</v>
       </c>
-      <c r="C105" s="29"/>
-      <c r="D105" s="30" t="s">
+      <c r="C105" s="31"/>
+      <c r="D105" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="E105" s="39"/>
-      <c r="F105" s="39"/>
-      <c r="G105" s="40"/>
+      <c r="E105" s="40"/>
+      <c r="F105" s="40"/>
+      <c r="G105" s="41"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A106" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="B106" s="38">
+      <c r="B106" s="42">
         <f>COUNTIF(F12:F101,"DATA_MISSING")</f>
         <v>0</v>
       </c>
-      <c r="C106" s="29"/>
-      <c r="D106" s="30" t="s">
+      <c r="C106" s="31"/>
+      <c r="D106" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="E106" s="39"/>
-      <c r="F106" s="39"/>
-      <c r="G106" s="40"/>
+      <c r="E106" s="40"/>
+      <c r="F106" s="40"/>
+      <c r="G106" s="41"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A107" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="B107" s="38">
+      <c r="B107" s="42">
         <f>SUM(E12:E101)</f>
         <v>28363930310</v>
       </c>
-      <c r="C107" s="29"/>
-      <c r="D107" s="30" t="s">
+      <c r="C107" s="31"/>
+      <c r="D107" s="39" t="s">
         <v>275</v>
       </c>
-      <c r="E107" s="39"/>
-      <c r="F107" s="39"/>
-      <c r="G107" s="40"/>
+      <c r="E107" s="40"/>
+      <c r="F107" s="40"/>
+      <c r="G107" s="41"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A108" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="B108" s="41">
+      <c r="B108" s="43">
         <f>B107/(B104-B106)</f>
         <v>315154781.22222221</v>
       </c>
-      <c r="C108" s="29"/>
-      <c r="D108" s="30" t="s">
+      <c r="C108" s="31"/>
+      <c r="D108" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="E108" s="39"/>
-      <c r="F108" s="39"/>
-      <c r="G108" s="40"/>
+      <c r="E108" s="40"/>
+      <c r="F108" s="40"/>
+      <c r="G108" s="41"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A110" s="36" t="s">
+      <c r="A110" s="32" t="s">
         <v>278</v>
       </c>
-      <c r="B110" s="29"/>
-      <c r="C110" s="29"/>
-      <c r="D110" s="29"/>
-      <c r="E110" s="29"/>
-      <c r="F110" s="29"/>
-      <c r="G110" s="29"/>
+      <c r="B110" s="31"/>
+      <c r="C110" s="31"/>
+      <c r="D110" s="31"/>
+      <c r="E110" s="31"/>
+      <c r="F110" s="31"/>
+      <c r="G110" s="31"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A111" s="35" t="s">
+      <c r="A111" s="33" t="s">
         <v>279</v>
       </c>
-      <c r="B111" s="29"/>
-      <c r="C111" s="29"/>
-      <c r="D111" s="29"/>
-      <c r="E111" s="29"/>
-      <c r="F111" s="29"/>
-      <c r="G111" s="29"/>
+      <c r="B111" s="31"/>
+      <c r="C111" s="31"/>
+      <c r="D111" s="31"/>
+      <c r="E111" s="31"/>
+      <c r="F111" s="31"/>
+      <c r="G111" s="31"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A112" s="35" t="s">
+      <c r="A112" s="33" t="s">
         <v>280</v>
       </c>
-      <c r="B112" s="29"/>
-      <c r="C112" s="29"/>
-      <c r="D112" s="29"/>
-      <c r="E112" s="29"/>
-      <c r="F112" s="29"/>
-      <c r="G112" s="29"/>
+      <c r="B112" s="31"/>
+      <c r="C112" s="31"/>
+      <c r="D112" s="31"/>
+      <c r="E112" s="31"/>
+      <c r="F112" s="31"/>
+      <c r="G112" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A112:G112"/>
-    <mergeCell ref="D106:G106"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A111:G111"/>
-    <mergeCell ref="A110:G110"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="B107:C107"/>
     <mergeCell ref="D107:G107"/>
@@ -6183,6 +6227,13 @@
     <mergeCell ref="B104:C104"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="D105:G105"/>
+    <mergeCell ref="A112:G112"/>
+    <mergeCell ref="D106:G106"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A111:G111"/>
+    <mergeCell ref="A110:G110"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6213,110 +6264,110 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="34" t="s">
         <v>283</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="34" t="s">
         <v>284</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A7" s="28"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
+      <c r="A7" s="30"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="30" t="s">
         <v>285</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="34" t="s">
         <v>286</v>
       </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="34" t="s">
         <v>287</v>
       </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A11" s="28"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="34" t="s">
         <v>289</v>
       </c>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
@@ -6335,7 +6386,7 @@
         <v>293</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>294</v>
@@ -6535,209 +6586,228 @@
         <v/>
       </c>
       <c r="G25" s="7" t="s">
-        <v>308</v>
+        <v>521</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="B28" s="32">
+        <v>309</v>
+      </c>
+      <c r="B28" s="35">
         <f>COUNT(C17:C24)</f>
         <v>8</v>
       </c>
-      <c r="C28" s="29"/>
-      <c r="D28" s="30" t="s">
-        <v>311</v>
-      </c>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="39" t="s">
+        <v>310</v>
+      </c>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="B29" s="32">
+        <v>311</v>
+      </c>
+      <c r="B29" s="35">
         <f>(B28-1)*0.1</f>
         <v>0.70000000000000007</v>
       </c>
-      <c r="C29" s="29"/>
-      <c r="D29" s="30" t="s">
-        <v>313</v>
-      </c>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="39" t="s">
+        <v>312</v>
+      </c>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="B30" s="32">
+        <v>313</v>
+      </c>
+      <c r="B30" s="35">
         <f>SMALL($C$17:$C$24,INT(B29)+1)</f>
         <v>315154781.22222221</v>
       </c>
-      <c r="C30" s="29"/>
-      <c r="D30" s="30" t="s">
-        <v>315</v>
-      </c>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="B31" s="32">
+        <v>315</v>
+      </c>
+      <c r="B31" s="35">
         <f>SMALL($C$17:$C$24,INT(B29)+2)</f>
         <v>317626170.95555562</v>
       </c>
-      <c r="C31" s="29"/>
-      <c r="D31" s="30" t="s">
-        <v>317</v>
-      </c>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="B32" s="33">
+        <v>317</v>
+      </c>
+      <c r="B32" s="38">
         <f t="shared" ref="B32" si="2">B30+(B29-INT(B29))*(B31-B30)</f>
         <v>316884754.0355556</v>
       </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="30" t="s">
-        <v>319</v>
-      </c>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="39" t="s">
+        <v>318</v>
+      </c>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="B33" s="33" t="str">
+        <v>319</v>
+      </c>
+      <c r="B33" s="38" t="str">
         <f>IF(C23&gt;=B32,"편입","제외")</f>
         <v>제외</v>
       </c>
-      <c r="C33" s="29"/>
-      <c r="D33" s="30" t="s">
-        <v>321</v>
-      </c>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="39" t="s">
+        <v>320</v>
+      </c>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="B34" s="32">
+        <v>321</v>
+      </c>
+      <c r="B34" s="35">
         <f>(C23/B32-1)*100</f>
         <v>-0.54593122303993047</v>
       </c>
-      <c r="C34" s="29"/>
-      <c r="D34" s="30" t="s">
-        <v>323</v>
-      </c>
-      <c r="E34" s="29"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="29"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="39" t="s">
+        <v>322</v>
+      </c>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="B35" s="32">
+        <v>323</v>
+      </c>
+      <c r="B35" s="35">
         <f>COUNTIF($C$17:$C$24,"&lt;"&amp;B32)</f>
         <v>1</v>
       </c>
-      <c r="C35" s="29"/>
-      <c r="D35" s="30" t="s">
+      <c r="C35" s="31"/>
+      <c r="D35" s="39" t="s">
+        <v>324</v>
+      </c>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A37" s="30" t="s">
         <v>325</v>
       </c>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="29"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A37" s="28" t="s">
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A38" s="34" t="s">
         <v>326</v>
       </c>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A38" s="31" t="s">
+      <c r="B38" s="31"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A39" s="34" t="s">
         <v>327</v>
       </c>
-      <c r="B38" s="29"/>
-      <c r="C38" s="29"/>
-      <c r="D38" s="29"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29"/>
-      <c r="G38" s="29"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A39" s="31" t="s">
+      <c r="B39" s="31"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A40" s="34" t="s">
         <v>328</v>
       </c>
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
-      <c r="D39" s="29"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="29"/>
-      <c r="G39" s="29"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A40" s="31" t="s">
-        <v>329</v>
-      </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A41" s="34" t="s">
-        <v>507</v>
-      </c>
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="29"/>
-      <c r="G41" s="29"/>
+      <c r="A41" s="36" t="s">
+        <v>506</v>
+      </c>
+      <c r="B41" s="31"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="B43" s="33">
+        <v>329</v>
+      </c>
+      <c r="B43" s="38">
         <f>CEILING(1/0.1,1)+1</f>
         <v>11</v>
       </c>
-      <c r="C43" s="29"/>
+      <c r="C43" s="31"/>
+      <c r="G43" t="s">
+        <v>522</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="A5:G5"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A40:G40"/>
@@ -6754,22 +6824,6 @@
     <mergeCell ref="D32:G32"/>
     <mergeCell ref="A37:G37"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6791,180 +6845,180 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A4" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" s="34" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="31" t="s">
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6" s="34" t="s">
         <v>333</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" s="31" t="s">
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" s="34" t="s">
         <v>334</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" s="31" t="s">
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A8" s="30"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A9" s="30" t="s">
         <v>335</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" s="28"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9" s="28" t="s">
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A11" s="32" t="s">
         <v>336</v>
       </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A11" s="36" t="s">
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A12" s="33" t="s">
         <v>337</v>
       </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A12" s="35" t="s">
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A13" s="33" t="s">
         <v>338</v>
       </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A13" s="35" t="s">
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A14" s="33" t="s">
         <v>339</v>
       </c>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A14" s="35" t="s">
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A15" s="33" t="s">
         <v>340</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A15" s="35" t="s">
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A16" s="33" t="s">
         <v>341</v>
       </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A16" s="35" t="s">
-        <v>342</v>
-      </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="E19" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="F19" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>348</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>349</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>151</v>
@@ -6973,13 +7027,13 @@
     <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20" s="5"/>
       <c r="B20" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="10" t="s">
         <v>351</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>352</v>
       </c>
       <c r="E20" s="19">
         <v>0.16666666666666666</v>
@@ -6997,13 +7051,13 @@
     <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" s="5"/>
       <c r="B21" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>354</v>
-      </c>
       <c r="D21" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E21" s="19">
         <v>0.16666666666666666</v>
@@ -7021,13 +7075,13 @@
     <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" s="5"/>
       <c r="B22" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>356</v>
-      </c>
       <c r="D22" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E22" s="19">
         <v>0.16666666666666666</v>
@@ -7045,13 +7099,13 @@
     <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23" s="5"/>
       <c r="B23" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>357</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>358</v>
       </c>
       <c r="E23" s="19">
         <v>0.16666666666666666</v>
@@ -7069,13 +7123,13 @@
     <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" s="5"/>
       <c r="B24" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E24" s="19">
         <v>0.16666666666666666</v>
@@ -7093,13 +7147,13 @@
     <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" s="5"/>
       <c r="B25" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E25" s="19">
         <v>0.16666666666666666</v>
@@ -7116,19 +7170,19 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="D26" s="20" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E26" s="21">
         <f>SUM(E20:E25)</f>
         <v>0.99999999999999989</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.45">
@@ -7137,13 +7191,13 @@
         <v>291</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>123</v>
@@ -7156,16 +7210,16 @@
     <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" s="5"/>
       <c r="B30" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F30" s="19">
         <f>VLOOKUP(E30,$B$20:$G$25,6,FALSE)</f>
@@ -7177,16 +7231,16 @@
     <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" s="5"/>
       <c r="B31" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F31" s="19">
         <f t="shared" ref="F31:F44" si="2">VLOOKUP(E31,$B$20:$G$25,6,FALSE)</f>
@@ -7198,16 +7252,16 @@
     <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" s="5"/>
       <c r="B32" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C32" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="E32" s="5" t="s">
         <v>352</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>353</v>
       </c>
       <c r="F32" s="19">
         <f t="shared" si="2"/>
@@ -7219,16 +7273,16 @@
     <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" s="5"/>
       <c r="B33" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C33" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>352</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>353</v>
       </c>
       <c r="F33" s="19">
         <f t="shared" si="2"/>
@@ -7240,16 +7294,16 @@
     <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" s="5"/>
       <c r="B34" s="10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C34" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>352</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>353</v>
       </c>
       <c r="F34" s="19">
         <f t="shared" si="2"/>
@@ -7261,16 +7315,16 @@
     <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35" s="5"/>
       <c r="B35" s="10" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F35" s="19">
         <f t="shared" si="2"/>
@@ -7282,16 +7336,16 @@
     <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" s="5"/>
       <c r="B36" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F36" s="19">
         <f t="shared" si="2"/>
@@ -7303,16 +7357,16 @@
     <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" s="5"/>
       <c r="B37" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F37" s="19">
         <f t="shared" si="2"/>
@@ -7327,13 +7381,13 @@
         <v>295</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F38" s="19">
         <f t="shared" si="2"/>
@@ -7348,13 +7402,13 @@
         <v>297</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F39" s="19">
         <f t="shared" si="2"/>
@@ -7369,13 +7423,13 @@
         <v>304</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F40" s="19">
         <f t="shared" si="2"/>
@@ -7390,13 +7444,13 @@
         <v>298</v>
       </c>
       <c r="C41" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="E41" s="5" t="s">
         <v>358</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>359</v>
       </c>
       <c r="F41" s="19">
         <f t="shared" si="2"/>
@@ -7411,13 +7465,13 @@
         <v>300</v>
       </c>
       <c r="C42" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="E42" s="5" t="s">
         <v>358</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>359</v>
       </c>
       <c r="F42" s="19">
         <f t="shared" si="2"/>
@@ -7432,13 +7486,13 @@
         <v>301</v>
       </c>
       <c r="C43" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="E43" s="5" t="s">
         <v>358</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>359</v>
       </c>
       <c r="F43" s="19">
         <f t="shared" si="2"/>
@@ -7453,129 +7507,134 @@
         <v>302</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F44" s="19">
         <f t="shared" si="2"/>
         <v>0.16666666666666666</v>
       </c>
       <c r="G44" s="5"/>
-      <c r="H44" s="7"/>
+      <c r="H44" s="7" t="s">
+        <v>523</v>
+      </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="E45" s="20" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F45" s="21">
         <f>SUM(F30:F44)</f>
         <v>1.0000000000000002</v>
       </c>
+      <c r="H45" t="s">
+        <v>524</v>
+      </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A47" s="28" t="s">
+      <c r="A47" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="B47" s="31"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="31"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A48" s="34" t="s">
         <v>372</v>
       </c>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="29"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A48" s="31" t="s">
+      <c r="B48" s="31"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="31"/>
+      <c r="H48" s="31"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A49" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A49" s="31" t="s">
+      <c r="B49" s="31"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="31"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A50" s="34" t="s">
         <v>374</v>
       </c>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A50" s="31" t="s">
-        <v>375</v>
-      </c>
-      <c r="B50" s="29"/>
-      <c r="C50" s="29"/>
-      <c r="D50" s="29"/>
-      <c r="E50" s="29"/>
-      <c r="F50" s="29"/>
-      <c r="G50" s="29"/>
-      <c r="H50" s="29"/>
+      <c r="B50" s="31"/>
+      <c r="C50" s="31"/>
+      <c r="D50" s="31"/>
+      <c r="E50" s="31"/>
+      <c r="F50" s="31"/>
+      <c r="G50" s="31"/>
+      <c r="H50" s="31"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="B52" s="33" t="str">
+        <v>375</v>
+      </c>
+      <c r="B52" s="38" t="str">
         <f>INDEX($B$30:$B$44,MATCH(MAX($F$30:$F$44),$F$30:$F$44,0))</f>
         <v>KTOS</v>
       </c>
-      <c r="C52" s="29"/>
+      <c r="C52" s="31"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="B53" s="33">
+        <v>376</v>
+      </c>
+      <c r="B53" s="38">
         <f>MAX($F$30:$F$44)*100</f>
         <v>16.666666666666664</v>
       </c>
-      <c r="C53" s="29"/>
+      <c r="C53" s="31"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="B54" s="33">
+        <v>377</v>
+      </c>
+      <c r="B54" s="38">
         <f>VLOOKUP(INDEX($E$30:$E$44,MATCH(MAX($F$30:$F$44),$F$30:$F$44,0)),$B$20:$F$25,5,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="C54" s="29"/>
+      <c r="C54" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A48:H48"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A47:H47"/>
     <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="B52:C52"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7597,150 +7656,150 @@
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" s="34" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A4" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" s="31" t="s">
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" s="34" t="s">
         <v>381</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A6" s="31" t="s">
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" s="34" t="s">
         <v>382</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A7" s="31" t="s">
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" s="30"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A9" s="34" t="s">
         <v>383</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A8" s="28"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A9" s="31" t="s">
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A10" s="30"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A11" s="30" t="s">
         <v>384</v>
       </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A10" s="28"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A11" s="28" t="s">
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A12" s="34" t="s">
         <v>385</v>
       </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A12" s="31" t="s">
-        <v>386</v>
-      </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C15" s="22">
         <v>1530.5</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G15" s="22">
         <v>1507.2</v>
@@ -7752,37 +7811,37 @@
         <v>291</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>123</v>
       </c>
       <c r="E17" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="H17" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="I17" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="J17" s="4" t="s">
         <v>394</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="5"/>
       <c r="B18" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D18" s="19">
         <f>VLOOKUP($B18,'06 목표비중'!$B$30:$F$44,5,FALSE)</f>
@@ -7814,10 +7873,10 @@
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="5"/>
       <c r="B19" s="10" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D19" s="19">
         <f>VLOOKUP($B19,'06 목표비중'!$B$30:$F$44,5,FALSE)</f>
@@ -7849,10 +7908,10 @@
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="5"/>
       <c r="B20" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D20" s="19">
         <f>VLOOKUP($B20,'06 목표비중'!$B$30:$F$44,5,FALSE)</f>
@@ -7884,10 +7943,10 @@
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="5"/>
       <c r="B21" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D21" s="19">
         <f>VLOOKUP($B21,'06 목표비중'!$B$30:$F$44,5,FALSE)</f>
@@ -7919,10 +7978,10 @@
     <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="5"/>
       <c r="B22" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D22" s="19">
         <f>VLOOKUP($B22,'06 목표비중'!$B$30:$F$44,5,FALSE)</f>
@@ -7954,10 +8013,10 @@
     <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="5"/>
       <c r="B23" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D23" s="19">
         <f>VLOOKUP($B23,'06 목표비중'!$B$30:$F$44,5,FALSE)</f>
@@ -7989,10 +8048,10 @@
     <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="5"/>
       <c r="B24" s="10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D24" s="19">
         <f>VLOOKUP($B24,'06 목표비중'!$B$30:$F$44,5,FALSE)</f>
@@ -8024,10 +8083,10 @@
     <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="5"/>
       <c r="B25" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D25" s="19">
         <f>VLOOKUP($B25,'06 목표비중'!$B$30:$F$44,5,FALSE)</f>
@@ -8062,7 +8121,7 @@
         <v>295</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D26" s="19">
         <f>VLOOKUP($B26,'06 목표비중'!$B$30:$F$44,5,FALSE)</f>
@@ -8097,7 +8156,7 @@
         <v>297</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D27" s="19">
         <f>VLOOKUP($B27,'06 목표비중'!$B$30:$F$44,5,FALSE)</f>
@@ -8132,7 +8191,7 @@
         <v>298</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D28" s="19">
         <f>VLOOKUP($B28,'06 목표비중'!$B$30:$F$44,5,FALSE)</f>
@@ -8167,7 +8226,7 @@
         <v>300</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D29" s="19">
         <f>VLOOKUP($B29,'06 목표비중'!$B$30:$F$44,5,FALSE)</f>
@@ -8202,7 +8261,7 @@
         <v>301</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D30" s="19">
         <f>VLOOKUP($B30,'06 목표비중'!$B$30:$F$44,5,FALSE)</f>
@@ -8237,7 +8296,7 @@
         <v>302</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D31" s="19">
         <f>VLOOKUP($B31,'06 목표비중'!$B$30:$F$44,5,FALSE)</f>
@@ -8272,7 +8331,7 @@
         <v>304</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D32" s="19">
         <f>VLOOKUP($B32,'06 목표비중'!$B$30:$F$44,5,FALSE)</f>
@@ -8303,7 +8362,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="I33" s="20" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J33" s="19">
         <f>SUM(J18:J32)</f>
@@ -8316,71 +8375,71 @@
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A36" s="42" t="s">
-        <v>396</v>
-      </c>
-      <c r="B36" s="39"/>
-      <c r="C36" s="40"/>
+      <c r="A36" s="44" t="s">
+        <v>395</v>
+      </c>
+      <c r="B36" s="40"/>
+      <c r="C36" s="41"/>
       <c r="D36" s="23">
         <f>1000*J33</f>
         <v>1023.8015667579472</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A38" s="36" t="s">
+      <c r="A38" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="B38" s="29"/>
-      <c r="C38" s="29"/>
-      <c r="D38" s="29"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29"/>
-      <c r="G38" s="29"/>
-      <c r="H38" s="29"/>
-      <c r="I38" s="29"/>
-      <c r="J38" s="29"/>
+      <c r="B38" s="31"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
+      <c r="J38" s="31"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A39" s="35" t="s">
+      <c r="A39" s="33" t="s">
+        <v>396</v>
+      </c>
+      <c r="B39" s="31"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="31"/>
+      <c r="I39" s="31"/>
+      <c r="J39" s="31"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A40" s="33" t="s">
         <v>397</v>
       </c>
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
-      <c r="D39" s="29"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="29"/>
-      <c r="G39" s="29"/>
-      <c r="H39" s="29"/>
-      <c r="I39" s="29"/>
-      <c r="J39" s="29"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A40" s="35" t="s">
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A41" s="33" t="s">
         <v>398</v>
       </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A41" s="35" t="s">
-        <v>399</v>
-      </c>
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="29"/>
-      <c r="G41" s="29"/>
-      <c r="H41" s="29"/>
-      <c r="I41" s="29"/>
-      <c r="J41" s="29"/>
+      <c r="B41" s="31"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="31"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -8419,119 +8478,119 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="30" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="28" t="s">
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="34" t="s">
         <v>402</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="31" t="s">
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="34" t="s">
         <v>403</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" s="31" t="s">
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" s="34" t="s">
         <v>404</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A7" s="31" t="s">
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" s="30"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9" s="30" t="s">
         <v>405</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A8" s="28"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="28" t="s">
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10" s="34" t="s">
         <v>406</v>
       </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="31" t="s">
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A11" s="34" t="s">
         <v>407</v>
       </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A11" s="31" t="s">
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A12" s="30"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A13" s="30" t="s">
         <v>408</v>
       </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="28" t="s">
-        <v>409</v>
-      </c>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" s="4"/>
@@ -8539,16 +8598,16 @@
         <v>146</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>181</v>
       </c>
       <c r="E15" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>411</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>412</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>151</v>
@@ -8605,7 +8664,7 @@
         <v>788000</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E18" s="24">
         <f t="shared" ref="E18:E24" si="0">IF($B18&lt;$B$21,C18/5,C18)</f>
@@ -8615,7 +8674,9 @@
         <f t="shared" ref="F18:F24" si="1">E18/E17-1</f>
         <v>0</v>
       </c>
-      <c r="G18" s="7"/>
+      <c r="G18" s="7" t="s">
+        <v>525</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="5"/>
@@ -8626,7 +8687,7 @@
         <v>788000</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E19" s="24">
         <f t="shared" si="0"/>
@@ -8647,7 +8708,7 @@
         <v>788000</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E20" s="24">
         <f t="shared" si="0"/>
@@ -8678,7 +8739,9 @@
         <f t="shared" si="1"/>
         <v>0.13705583756345185</v>
       </c>
-      <c r="G21" s="7"/>
+      <c r="G21" s="7" t="s">
+        <v>526</v>
+      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="5"/>
@@ -8745,172 +8808,183 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="3" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A27" s="44" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A27" s="42" t="s">
-        <v>415</v>
-      </c>
-      <c r="B27" s="40"/>
+      <c r="B27" s="41"/>
       <c r="C27" s="26">
         <f>C21/C17-1</f>
         <v>-0.77258883248730958</v>
       </c>
-      <c r="D27" s="30" t="s">
+      <c r="D27" s="39" t="s">
+        <v>415</v>
+      </c>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A28" s="44" t="s">
         <v>416</v>
       </c>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A28" s="42" t="s">
-        <v>417</v>
-      </c>
-      <c r="B28" s="40"/>
+      <c r="B28" s="41"/>
       <c r="C28" s="26">
         <f>C21/E17-1</f>
         <v>0.13705583756345185</v>
       </c>
-      <c r="D28" s="30" t="s">
+      <c r="D28" s="39" t="s">
+        <v>417</v>
+      </c>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A29" s="44" t="s">
         <v>418</v>
       </c>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A29" s="42" t="s">
-        <v>419</v>
-      </c>
-      <c r="B29" s="40"/>
+      <c r="B29" s="41"/>
       <c r="C29" s="26">
         <f>C27-C28</f>
         <v>-0.90964467005076144</v>
       </c>
-      <c r="D29" s="30" t="s">
+      <c r="D29" s="39" t="s">
+        <v>419</v>
+      </c>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A30" s="44" t="s">
         <v>420</v>
       </c>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A30" s="42" t="s">
-        <v>421</v>
-      </c>
-      <c r="B30" s="40"/>
+      <c r="B30" s="41"/>
       <c r="C30" s="26">
         <f>C29*VLOOKUP("010120",'06 목표비중'!$B$30:$F$44,5,FALSE)</f>
         <v>-5.0535815002820075E-2</v>
       </c>
-      <c r="D30" s="30" t="s">
+      <c r="D30" s="39" t="s">
+        <v>421</v>
+      </c>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A32" s="32" t="s">
         <v>422</v>
       </c>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A32" s="36" t="s">
+      <c r="B32" s="31"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A33" s="33" t="s">
         <v>423</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A33" s="35" t="s">
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A34" s="33" t="s">
         <v>424</v>
       </c>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A34" s="35" t="s">
+      <c r="B34" s="31"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A35" s="33" t="s">
         <v>425</v>
       </c>
-      <c r="B34" s="29"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="29"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A35" s="35" t="s">
+      <c r="B35" s="31"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A36" s="32"/>
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A37" s="32" t="s">
         <v>426</v>
       </c>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="29"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A36" s="36"/>
-      <c r="B36" s="29"/>
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="29"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A37" s="36" t="s">
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A38" s="33" t="s">
         <v>427</v>
       </c>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A38" s="35" t="s">
+      <c r="B38" s="31"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A39" s="33" t="s">
         <v>428</v>
       </c>
-      <c r="B38" s="29"/>
-      <c r="C38" s="29"/>
-      <c r="D38" s="29"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29"/>
-      <c r="G38" s="29"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A39" s="35" t="s">
+      <c r="B39" s="31"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A40" s="33" t="s">
         <v>429</v>
       </c>
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
-      <c r="D39" s="29"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="29"/>
-      <c r="G39" s="29"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A40" s="35" t="s">
-        <v>430</v>
-      </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="A5:G5"/>
     <mergeCell ref="A38:G38"/>
     <mergeCell ref="D29:G29"/>
     <mergeCell ref="A10:G10"/>
@@ -8927,17 +9001,6 @@
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8946,7 +9009,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -8960,61 +9023,61 @@
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A4" s="32" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" s="36" t="s">
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" s="33" t="s">
         <v>433</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="35" t="s">
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6" s="33" t="s">
         <v>434</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" s="35" t="s">
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" s="33" t="s">
         <v>435</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" s="35" t="s">
-        <v>436</v>
-      </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="4"/>
@@ -9022,27 +9085,27 @@
         <v>97</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>441</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="10" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>102</v>
@@ -9057,290 +9120,353 @@
         <f>'02 자료마감일'!B26</f>
         <v>2026-06-23</v>
       </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="12"/>
+      <c r="F10" s="45">
+        <v>46196</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>511</v>
+      </c>
       <c r="H10" s="7"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="C11" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="10" t="s">
         <v>446</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>447</v>
       </c>
       <c r="E11" s="17">
         <f>'03-04 거래대금·ADTV90'!B108</f>
         <v>315154781.22222221</v>
       </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="12"/>
+      <c r="F11" s="7">
+        <v>315154781.22222221</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>511</v>
+      </c>
       <c r="H11" s="7"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>445</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="10" t="s">
         <v>449</v>
       </c>
-      <c r="D12" s="10" t="s">
-        <v>450</v>
-      </c>
-      <c r="E12" s="43">
+      <c r="E12" s="28">
         <f>'03-04 거래대금·ADTV90'!B104-'03-04 거래대금·ADTV90'!B106</f>
         <v>90</v>
       </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="7"/>
+      <c r="F12" s="7">
+        <v>90</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>512</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="10" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>117</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E13" s="17">
         <f>'05 P10·편입판정'!B32</f>
         <v>316884754.0355556</v>
       </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="12"/>
+      <c r="F13" s="7">
+        <v>316884754.0355556</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>511</v>
+      </c>
       <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>117</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E14" s="7" t="str">
         <f>'05 P10·편입판정'!B33</f>
         <v>제외</v>
       </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="12"/>
+      <c r="F14" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>511</v>
+      </c>
       <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" s="10" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>117</v>
       </c>
       <c r="C15" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="D15" s="10" t="s">
         <v>456</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>457</v>
       </c>
       <c r="E15" s="7">
         <f>'05 P10·편입판정'!B35</f>
         <v>1</v>
       </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="12"/>
+      <c r="F15" s="7">
+        <v>1</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>511</v>
+      </c>
       <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>117</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E16" s="7">
         <f>'05 P10·편입판정'!B43</f>
         <v>11</v>
       </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="12"/>
+      <c r="F16" s="7">
+        <v>11</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>511</v>
+      </c>
       <c r="H16" s="7"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" s="10" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>122</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>461</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>462</v>
       </c>
       <c r="E17" s="19">
         <f>'06 목표비중'!F45</f>
         <v>1.0000000000000002</v>
       </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="7"/>
+      <c r="F17" s="7">
+        <v>1</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>514</v>
+      </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" s="10" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>122</v>
       </c>
       <c r="C18" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="D18" s="10" t="s">
         <v>464</v>
       </c>
-      <c r="D18" s="10" t="s">
-        <v>465</v>
-      </c>
-      <c r="E18" s="44">
+      <c r="E18" s="29">
         <f>'06 목표비중'!B53</f>
         <v>16.666666666666664</v>
       </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="7"/>
+      <c r="F18" s="7">
+        <v>16.666666666666661</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>515</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" s="10" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>127</v>
       </c>
       <c r="C19" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>467</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>468</v>
       </c>
       <c r="E19" s="17">
         <f>'07 지수레벨'!D36</f>
         <v>1023.8015667579472</v>
       </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="7"/>
+      <c r="F19" s="7">
+        <v>1023.8015667579469</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20" s="10" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>132</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>465</v>
-      </c>
-      <c r="E20" s="44">
+        <v>464</v>
+      </c>
+      <c r="E20" s="29">
         <f>'08 분할효과'!C27*100</f>
         <v>-77.258883248730953</v>
       </c>
-      <c r="F20" s="7"/>
-      <c r="G20" s="12"/>
+      <c r="F20" s="7">
+        <v>-77.258883248730953</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>511</v>
+      </c>
       <c r="H20" s="7"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" s="10" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>132</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>465</v>
-      </c>
-      <c r="E21" s="44">
+        <v>464</v>
+      </c>
+      <c r="E21" s="29">
         <f>'08 분할효과'!C28*100</f>
         <v>13.705583756345185</v>
       </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="7"/>
+      <c r="F21" s="7">
+        <v>13.705583756345179</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>517</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23" s="3" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A24" s="44" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A24" s="42" t="s">
+      <c r="B24" s="40"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="38">
+        <f>COUNTIF($G$10:$G$21,"일치")</f>
+        <v>12</v>
+      </c>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A25" s="44" t="s">
         <v>474</v>
       </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="33">
-        <f>COUNTIF($G$10:$G$21,"일치")</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A25" s="42" t="s">
-        <v>475</v>
-      </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="33">
+      <c r="B25" s="40"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="38">
         <f>COUNTIF($G$10:$G$21,"불일치")</f>
         <v>0</v>
       </c>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A26" s="42" t="s">
-        <v>476</v>
-      </c>
-      <c r="B26" s="39"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="33" t="str">
+      <c r="A26" s="44" t="s">
+        <v>475</v>
+      </c>
+      <c r="B26" s="40"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="38" t="str">
         <f>IF(COUNTA($F$10:$F$21)&lt;12,"코드값 미입력 — 봉인 파일 개봉 후 F·G열을 채우면 결론이 자동 산출됩니다",IF(D25=0,"12개 항목 전부 일치 — 구현이 규칙대로 작동함을 수기 검산으로 확인","불일치 "&amp;D25&amp;"건 — H열에 원인을 기록할 것"))</f>
-        <v>코드값 미입력 — 봉인 파일 개봉 후 F·G열을 채우면 결론이 자동 산출됩니다</v>
-      </c>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
+        <v>12개 항목 전부 일치 — 구현이 규칙대로 작동함을 수기 검산으로 확인</v>
+      </c>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>518</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="10">
